--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,07</t>
+          <t>-6,86; 0,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,96</t>
+          <t>0,83; 9,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 0,73</t>
+          <t>-9,81; 0,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 2,81</t>
+          <t>-8,75; 3,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -0,66</t>
+          <t>-7,21; -0,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,46</t>
+          <t>-1,69; 5,64</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 6,53</t>
+          <t>-34,5; 4,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 62,87</t>
+          <t>4,49; 59,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 2,45</t>
+          <t>-27,58; 1,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 9,06</t>
+          <t>-24,58; 12,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -2,89</t>
+          <t>-26,43; -2,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 22,29</t>
+          <t>-6,37; 23,79</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 1,01</t>
+          <t>-5,7; 1,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -0,22</t>
+          <t>-12,16; -0,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,06</t>
+          <t>-8,11; 0,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,08</t>
+          <t>-2,49; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -0,35</t>
+          <t>-5,95; -0,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 0,82</t>
+          <t>-10,51; 0,78</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 6,39</t>
+          <t>-30,25; 8,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -1,22</t>
+          <t>-65,88; -2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,07; -0,15</t>
+          <t>-25,89; 0,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 18,47</t>
+          <t>-7,94; 18,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,69; -1,56</t>
+          <t>-23,1; -1,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,88; 3,42</t>
+          <t>-43,09; 3,36</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,94</t>
+          <t>-4,92; 2,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,47</t>
+          <t>-1,32; 6,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 2,47</t>
+          <t>-6,78; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 7,04</t>
+          <t>-14,4; 6,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,14</t>
+          <t>-4,35; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,01</t>
+          <t>-6,42; 5,23</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 23,33</t>
+          <t>-28,71; 22,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 51,11</t>
+          <t>-7,92; 53,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 11,0</t>
+          <t>-24,48; 9,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 28,3</t>
+          <t>-54,53; 27,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 5,92</t>
+          <t>-20,59; 6,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 25,47</t>
+          <t>-30,5; 26,86</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,31</t>
+          <t>-5,48; 1,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,8</t>
+          <t>-2,51; 4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,28</t>
+          <t>-6,76; 1,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 7,51</t>
+          <t>-3,45; 7,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,23</t>
+          <t>-4,99; 0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,42</t>
+          <t>-0,85; 5,26</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 8,62</t>
+          <t>-28,61; 8,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 30,36</t>
+          <t>-12,4; 29,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 5,36</t>
+          <t>-22,3; 5,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 28,08</t>
+          <t>-11,37; 28,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 1,02</t>
+          <t>-20,46; 2,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 24,87</t>
+          <t>-3,3; 24,07</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,2</t>
+          <t>-3,79; -0,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,42</t>
+          <t>-3,43; 2,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,28</t>
+          <t>-5,43; -1,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,53</t>
+          <t>-5,15; 3,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,38</t>
+          <t>-4,24; -1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,48</t>
+          <t>-2,71; 2,51</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -1,36</t>
+          <t>-21,14; -2,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 14,75</t>
+          <t>-19,55; 15,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -4,53</t>
+          <t>-18,12; -3,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 12,49</t>
+          <t>-16,96; 12,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,43; -6,21</t>
+          <t>-17,58; -5,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 10,84</t>
+          <t>-11,77; 10,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 0,78</t>
+          <t>-7,17; 0,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,73</t>
+          <t>0,85; 9,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 0,28</t>
+          <t>-9,82; 0,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 3,81</t>
+          <t>-4,81; 4,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,53</t>
+          <t>-7,09; -0,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,64</t>
+          <t>-0,44; 6,29</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,55%</t>
+          <t>-0,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 4,82</t>
+          <t>-35,32; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 59,7</t>
+          <t>4,2; 60,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 1,03</t>
+          <t>-28,27; 0,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 12,15</t>
+          <t>-13,22; 14,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,43; -2,29</t>
+          <t>-26,23; -2,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 23,79</t>
+          <t>-1,8; 26,87</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-1,71</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 1,24</t>
+          <t>-5,63; 1,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; -0,36</t>
+          <t>-4,82; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,23</t>
+          <t>-7,97; -0,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,1</t>
+          <t>-2,64; 4,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,43</t>
+          <t>-5,7; -0,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 0,78</t>
+          <t>-2,8; 2,39</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-27,59%</t>
+          <t>-9,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-1,14%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 8,03</t>
+          <t>-29,59; 7,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -2,48</t>
+          <t>-25,69; 10,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 0,82</t>
+          <t>-25,13; -0,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 18,2</t>
+          <t>-8,44; 17,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -1,09</t>
+          <t>-23,0; -1,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 3,36</t>
+          <t>-11,15; 10,72</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>4,14</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 2,76</t>
+          <t>-4,89; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 6,94</t>
+          <t>-1,48; 6,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 2,23</t>
+          <t>-7,1; 2,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 6,97</t>
+          <t>1,13; 10,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,37</t>
+          <t>-4,71; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,23</t>
+          <t>1,25; 6,9</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,91%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 22,35</t>
+          <t>-29,33; 20,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 53,12</t>
+          <t>-9,3; 48,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 9,81</t>
+          <t>-25,07; 9,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,53; 27,99</t>
+          <t>3,98; 43,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 6,89</t>
+          <t>-21,59; 7,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 26,86</t>
+          <t>5,58; 37,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>3,15</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,45</t>
+          <t>-5,8; 1,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,65</t>
+          <t>-2,78; 4,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 1,53</t>
+          <t>-6,67; 1,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,76</t>
+          <t>1,37; 8,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,5</t>
+          <t>-5,11; 0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,26</t>
+          <t>0,4; 5,51</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 8,41</t>
+          <t>-29,44; 7,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 29,32</t>
+          <t>-14,14; 27,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 5,59</t>
+          <t>-21,73; 6,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 28,1</t>
+          <t>4,65; 31,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 2,2</t>
+          <t>-20,65; 1,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 24,07</t>
+          <t>1,49; 24,65</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,37</t>
+          <t>-3,84; -0,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,6</t>
+          <t>-0,77; 3,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -1,12</t>
+          <t>-5,73; -1,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,41</t>
+          <t>1,19; 5,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -1,26</t>
+          <t>-4,22; -1,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,51</t>
+          <t>0,81; 3,74</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -2,3</t>
+          <t>-21,53; -1,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 15,55</t>
+          <t>-4,37; 20,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -3,97</t>
+          <t>-18,83; -4,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 12,05</t>
+          <t>3,9; 19,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -5,58</t>
+          <t>-17,68; -6,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 10,88</t>
+          <t>3,43; 16,74</t>
         </is>
       </c>
     </row>
